--- a/2018/South2/South2_members_final.xlsx
+++ b/2018/South2/South2_members_final.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
